--- a/02_DIA_inicio_2026_analisis_assets/rbd_9730_colegio-antu_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9730_colegio-antu_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0DF52B2-E8DF-4B1A-B01B-41E9F2E2D75D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7DD17F8-8579-450E-B032-1B052CD4440C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0731CBCB-93E6-4D65-8E8C-C43C9F4D8014}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12FE9C46-FC2D-4D31-A92F-82B13B107A13}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69DF590A-6BD7-4518-8E4B-1D1A6402BA3B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB49FC4C-041F-4B89-AC0C-C6CF20B28706}"/>
 </file>